--- a/reference/RefMappings.xlsx
+++ b/reference/RefMappings.xlsx
@@ -712,7 +712,11 @@
           <t>441X</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr"/>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Auto and other motor vehicle dealers</t>
+        </is>
+      </c>
       <c r="C4" s="7" t="n"/>
       <c r="D4" s="6" t="n">
         <v>30</v>
@@ -803,7 +807,11 @@
           <t>4451</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr"/>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>Grocery stores</t>
+        </is>
+      </c>
       <c r="C9" s="7" t="n"/>
       <c r="D9" s="6" t="n">
         <v>80</v>
@@ -875,7 +883,11 @@
           <t>44W72</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr"/>
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>Retail trade and food services, excluding motor vehicle and parts dealers and gasoline stations</t>
+        </is>
+      </c>
       <c r="C13" s="7" t="n"/>
       <c r="D13" s="6" t="n">
         <v>120</v>
@@ -909,7 +921,11 @@
           <t>44Y72</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr"/>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>Retail trade and food services, excluding motor vehicle and parts dealers</t>
+        </is>
+      </c>
       <c r="C15" s="7" t="n"/>
       <c r="D15" s="6" t="n">
         <v>140</v>
@@ -924,7 +940,11 @@
           <t>44Z72</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr"/>
+      <c r="B16" s="6" t="inlineStr">
+        <is>
+          <t>Retail trade and food services, excluding gasoline stations</t>
+        </is>
+      </c>
       <c r="C16" s="7" t="n"/>
       <c r="D16" s="6" t="n">
         <v>150</v>

--- a/reference/RefMappings.xlsx
+++ b/reference/RefMappings.xlsx
@@ -540,7 +540,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Yellow cells need your input: CategoryName for codes not in Table 3.1, CategoryGroup for every row, and IsAggregate where it is flagged for confirmation.</t>
+          <t>Yellow cells need your input: CategoryGroup for every row, and IsAggregate where it is flagged for confirmation. CategoryName is complete — the five codes that are not in Table 3.1 (441X, 4451, 44W72, 44Y72, 44Z72) were resolved from the FRED MARTS series titles, which carry the Census category code in the series ID.</t>
         </is>
       </c>
     </row>
